--- a/docs/vendors/chemito/PMIDTC_CIPLAPIS.xlsx
+++ b/docs/vendors/chemito/PMIDTC_CIPLAPIS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energygna-my.sharepoint.com/personal/raman_sharma_gna_energy/Documents/Desktop/BMS2/BMS/docs/vendors/chemito/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_25535FFD175E6FCFCB3D45214BAC33A9CAE27E25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14D7A69-8B06-4C34-9559-50EA4CAF0528}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_25535FFD175E6FCFCB3D45214BAC33A9CAE27E25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50C70FEC-9EF2-4285-B4B2-8ECF14F44998}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="-14430" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -358,9 +358,6 @@
     <t>dt:[string]Device type, optional parameter,n9m device is not transmitted, CMS device is transmitted dt=MDVR</t>
   </si>
   <si>
-    <t>"url": "http://15.252.130.159:12060/live.flv?devid=006000E4C0&amp;chl=1&amp;st=1&amp;audio=1&amp;svrip=127.0.0.1&amp;svrport=17891&amp;token=jYZi%2FP%2FAJPTDkBH%2F9lejs6Wie0zTACJJbNvi7Smh2eNXq1g\""</t>
-  </si>
-  <si>
     <t>data:Video address</t>
   </si>
   <si>
@@ -629,6 +626,9 @@
   </si>
   <si>
     <t>Rear radar alarm</t>
+  </si>
+  <si>
+    <t>"url": "http://15.252.130.159:22060/live.flv?devid=006000E4C0&amp;chl=1&amp;st=1&amp;audio=1&amp;svrip=127.0.0.1&amp;svrport=17891&amp;token=jYZi%2FP%2FAJPTDkBH%2F9lejs6Wie0zTACJJbNvi7Smh2eNXq1g\""</t>
   </si>
 </sst>
 </file>
@@ -840,16 +840,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1457,10 +1457,10 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="18"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
@@ -1487,7 +1487,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="18">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1495,25 +1495,25 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="18"/>
+      <c r="A9" s="17"/>
       <c r="B9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="18"/>
+      <c r="A10" s="17"/>
       <c r="B10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18">
-      <c r="A11" s="18"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -1521,13 +1521,13 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="18"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -1535,43 +1535,43 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="18">
-      <c r="A15" s="18"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="18"/>
+      <c r="A16" s="17"/>
       <c r="B16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="18"/>
+      <c r="A17" s="17"/>
       <c r="B17" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="18">
-      <c r="A18" s="18"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="18"/>
+      <c r="A19" s="17"/>
       <c r="B19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18">
-      <c r="A20" s="18"/>
+      <c r="A20" s="17"/>
       <c r="B20" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="7" t="s">
@@ -1579,13 +1579,13 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="18"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="18"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="8" t="s">
         <v>26</v>
       </c>
@@ -1596,10 +1596,10 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="16"/>
+      <c r="B25" s="18"/>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
@@ -1626,7 +1626,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" ht="18">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1634,37 +1634,37 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="18"/>
+      <c r="A30" s="17"/>
       <c r="B30" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="18"/>
+      <c r="A31" s="17"/>
       <c r="B31" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="18"/>
+      <c r="A32" s="17"/>
       <c r="B32" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="18"/>
+      <c r="A33" s="17"/>
       <c r="B33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="18">
-      <c r="A34" s="18"/>
+      <c r="A34" s="17"/>
       <c r="B34" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="7" t="s">
@@ -1672,25 +1672,25 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="18"/>
+      <c r="A36" s="17"/>
       <c r="B36" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="18"/>
+      <c r="A37" s="17"/>
       <c r="B37" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="18"/>
+      <c r="A38" s="17"/>
       <c r="B38" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="18">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -1698,115 +1698,115 @@
       </c>
     </row>
     <row r="40" spans="1:2" ht="18">
-      <c r="A40" s="18"/>
+      <c r="A40" s="17"/>
       <c r="B40" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="18"/>
+      <c r="A41" s="17"/>
       <c r="B41" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="18">
-      <c r="A42" s="18"/>
+      <c r="A42" s="17"/>
       <c r="B42" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="18">
-      <c r="A43" s="18"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="18"/>
+      <c r="A44" s="17"/>
       <c r="B44" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="18"/>
+      <c r="A45" s="17"/>
       <c r="B45" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="18"/>
+      <c r="A46" s="17"/>
       <c r="B46" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="18"/>
+      <c r="A47" s="17"/>
       <c r="B47" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="18"/>
+      <c r="A48" s="17"/>
       <c r="B48" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="18"/>
+      <c r="A49" s="17"/>
       <c r="B49" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="18"/>
+      <c r="A50" s="17"/>
       <c r="B50" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="18"/>
+      <c r="A51" s="17"/>
       <c r="B51" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="18"/>
+      <c r="A52" s="17"/>
       <c r="B52" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="18"/>
+      <c r="A53" s="17"/>
       <c r="B53" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="18">
-      <c r="A54" s="18"/>
+      <c r="A54" s="17"/>
       <c r="B54" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="18">
-      <c r="A55" s="18"/>
+      <c r="A55" s="17"/>
       <c r="B55" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="18"/>
+      <c r="A56" s="17"/>
       <c r="B56" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="18">
-      <c r="A57" s="18"/>
+      <c r="A57" s="17"/>
       <c r="B57" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B58" s="7" t="s">
@@ -1814,67 +1814,67 @@
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="18"/>
+      <c r="A59" s="17"/>
       <c r="B59" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="18"/>
+      <c r="A60" s="17"/>
       <c r="B60" s="10" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="18"/>
+      <c r="A61" s="17"/>
       <c r="B61" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="18"/>
+      <c r="A62" s="17"/>
       <c r="B62" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="18"/>
+      <c r="A63" s="17"/>
       <c r="B63" s="10" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="18"/>
+      <c r="A64" s="17"/>
       <c r="B64" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="18"/>
+      <c r="A65" s="17"/>
       <c r="B65" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="18"/>
+      <c r="A66" s="17"/>
       <c r="B66" s="10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="18"/>
+      <c r="A67" s="17"/>
       <c r="B67" s="10" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="18"/>
+      <c r="A68" s="17"/>
       <c r="B68" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="18"/>
+      <c r="A69" s="17"/>
       <c r="B69" s="8" t="s">
         <v>26</v>
       </c>
@@ -1885,10 +1885,10 @@
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="16"/>
+      <c r="B71" s="18"/>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2" t="s">
@@ -1915,7 +1915,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" ht="18">
-      <c r="A75" s="18" t="s">
+      <c r="A75" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B75" s="5" t="s">
@@ -1923,79 +1923,79 @@
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="18"/>
+      <c r="A76" s="17"/>
       <c r="B76" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="18">
-      <c r="A77" s="18"/>
+      <c r="A77" s="17"/>
       <c r="B77" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="18"/>
+      <c r="A78" s="17"/>
       <c r="B78" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="18">
-      <c r="A79" s="18"/>
+      <c r="A79" s="17"/>
       <c r="B79" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="18">
-      <c r="A80" s="18"/>
+      <c r="A80" s="17"/>
       <c r="B80" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="18">
-      <c r="A81" s="18"/>
+      <c r="A81" s="17"/>
       <c r="B81" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="18"/>
+      <c r="A82" s="17"/>
       <c r="B82" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="18">
-      <c r="A83" s="18"/>
+      <c r="A83" s="17"/>
       <c r="B83" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="18">
-      <c r="A84" s="18"/>
+      <c r="A84" s="17"/>
       <c r="B84" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="18"/>
+      <c r="A85" s="17"/>
       <c r="B85" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="18"/>
+      <c r="A86" s="17"/>
       <c r="B86" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="18">
-      <c r="A87" s="18"/>
+      <c r="A87" s="17"/>
       <c r="B87" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="18" t="s">
+      <c r="A88" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B88" s="7" t="s">
@@ -2003,31 +2003,31 @@
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="18"/>
+      <c r="A89" s="17"/>
       <c r="B89" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="18"/>
+      <c r="A90" s="17"/>
       <c r="B90" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="18"/>
+      <c r="A91" s="17"/>
       <c r="B91" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="18"/>
+      <c r="A92" s="17"/>
       <c r="B92" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="18">
-      <c r="A93" s="18" t="s">
+      <c r="A93" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B93" s="5" t="s">
@@ -2035,133 +2035,133 @@
       </c>
     </row>
     <row r="94" spans="1:2" ht="18">
-      <c r="A94" s="18"/>
+      <c r="A94" s="17"/>
       <c r="B94" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="18"/>
+      <c r="A95" s="17"/>
       <c r="B95" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="18">
-      <c r="A96" s="18"/>
+      <c r="A96" s="17"/>
       <c r="B96" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="18">
-      <c r="A97" s="18"/>
+      <c r="A97" s="17"/>
       <c r="B97" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="18"/>
+      <c r="A98" s="17"/>
       <c r="B98" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="18"/>
+      <c r="A99" s="17"/>
       <c r="B99" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="18"/>
+      <c r="A100" s="17"/>
       <c r="B100" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="18"/>
+      <c r="A101" s="17"/>
       <c r="B101" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="18"/>
+      <c r="A102" s="17"/>
       <c r="B102" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="18"/>
+      <c r="A103" s="17"/>
       <c r="B103" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="18"/>
+      <c r="A104" s="17"/>
       <c r="B104" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="18"/>
+      <c r="A105" s="17"/>
       <c r="B105" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="18"/>
+      <c r="A106" s="17"/>
       <c r="B106" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="18"/>
+      <c r="A107" s="17"/>
       <c r="B107" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="18"/>
+      <c r="A108" s="17"/>
       <c r="B108" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="18"/>
+      <c r="A109" s="17"/>
       <c r="B109" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="18"/>
+      <c r="A110" s="17"/>
       <c r="B110" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="18">
-      <c r="A111" s="18"/>
+      <c r="A111" s="17"/>
       <c r="B111" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="18">
-      <c r="A112" s="18"/>
+      <c r="A112" s="17"/>
       <c r="B112" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="18"/>
+      <c r="A113" s="17"/>
       <c r="B113" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="18">
-      <c r="A114" s="18"/>
+      <c r="A114" s="17"/>
       <c r="B114" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="18" t="s">
+      <c r="A115" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B115" s="7" t="s">
@@ -2169,85 +2169,85 @@
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="18"/>
+      <c r="A116" s="17"/>
       <c r="B116" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="18"/>
+      <c r="A117" s="17"/>
       <c r="B117" s="10" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="18"/>
+      <c r="A118" s="17"/>
       <c r="B118" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="18"/>
+      <c r="A119" s="17"/>
       <c r="B119" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="18"/>
+      <c r="A120" s="17"/>
       <c r="B120" s="10" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="18"/>
+      <c r="A121" s="17"/>
       <c r="B121" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="18"/>
+      <c r="A122" s="17"/>
       <c r="B122" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="18"/>
+      <c r="A123" s="17"/>
       <c r="B123" s="10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="18"/>
+      <c r="A124" s="17"/>
       <c r="B124" s="10" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="18"/>
+      <c r="A125" s="17"/>
       <c r="B125" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="18"/>
+      <c r="A126" s="17"/>
       <c r="B126" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="18"/>
+      <c r="A127" s="17"/>
       <c r="B127" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="18"/>
+      <c r="A128" s="17"/>
       <c r="B128" s="10" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="18"/>
+      <c r="A129" s="17"/>
       <c r="B129" s="8" t="s">
         <v>26</v>
       </c>
@@ -2258,13 +2258,13 @@
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="17" t="s">
+      <c r="A131" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B131" s="16"/>
+      <c r="B131" s="18"/>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="18" t="s">
+      <c r="A132" s="17" t="s">
         <v>3</v>
       </c>
       <c r="B132" s="7" t="s">
@@ -2272,13 +2272,13 @@
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="18"/>
+      <c r="A133" s="17"/>
       <c r="B133" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="18" t="s">
+      <c r="A134" s="17" t="s">
         <v>81</v>
       </c>
       <c r="B134" t="s">
@@ -2286,19 +2286,19 @@
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="18"/>
+      <c r="A135" s="17"/>
       <c r="B135" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="18"/>
+      <c r="A136" s="17"/>
       <c r="B136" s="10" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="18"/>
+      <c r="A137" s="17"/>
       <c r="B137" s="8" t="s">
         <v>85</v>
       </c>
@@ -2328,7 +2328,7 @@
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="18" t="s">
+      <c r="A141" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B141" s="7" t="s">
@@ -2336,43 +2336,43 @@
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="18"/>
+      <c r="A142" s="17"/>
       <c r="B142" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="18"/>
+      <c r="A143" s="17"/>
       <c r="B143" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="18"/>
+      <c r="A144" s="17"/>
       <c r="B144" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="18"/>
+      <c r="A145" s="17"/>
       <c r="B145" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="18"/>
+      <c r="A146" s="17"/>
       <c r="B146" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="18"/>
+      <c r="A147" s="17"/>
       <c r="B147" s="8" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="18">
-      <c r="A148" s="18" t="s">
+      <c r="A148" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B148" s="5" t="s">
@@ -2380,73 +2380,73 @@
       </c>
     </row>
     <row r="149" spans="1:2" ht="18">
-      <c r="A149" s="18"/>
+      <c r="A149" s="17"/>
       <c r="B149" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="18"/>
+      <c r="A150" s="17"/>
       <c r="B150" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="17.25">
-      <c r="A151" s="18"/>
+      <c r="A151" s="17"/>
       <c r="B151" s="14" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="18">
-      <c r="A152" s="18"/>
+      <c r="A152" s="17"/>
       <c r="B152" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="18"/>
+      <c r="A153" s="17"/>
       <c r="B153" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="18">
-      <c r="A154" s="18"/>
+      <c r="A154" s="17"/>
       <c r="B154" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="18" t="s">
+      <c r="A155" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B155" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="17"/>
+      <c r="B156" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="18"/>
-      <c r="B156" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="18"/>
+      <c r="A157" s="17"/>
       <c r="B157" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B158" s="16"/>
+      <c r="A158" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B158" s="18"/>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2454,7 +2454,7 @@
         <v>200</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2462,7 +2462,7 @@
         <v>201</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2470,7 +2470,7 @@
         <v>202</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2478,7 +2478,7 @@
         <v>203</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2486,7 +2486,7 @@
         <v>204</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2494,7 +2494,7 @@
         <v>205</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2502,7 +2502,7 @@
         <v>206</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2510,7 +2510,7 @@
         <v>207</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2518,7 +2518,7 @@
         <v>208</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2526,7 +2526,7 @@
         <v>209</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2534,7 +2534,7 @@
         <v>210</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2542,7 +2542,7 @@
         <v>211</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2550,7 +2550,7 @@
         <v>212</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2558,7 +2558,7 @@
         <v>213</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2566,7 +2566,7 @@
         <v>214</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2574,7 +2574,7 @@
         <v>215</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2582,7 +2582,7 @@
         <v>216</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -2590,7 +2590,7 @@
         <v>217</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -2598,7 +2598,7 @@
         <v>218</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -2606,7 +2606,7 @@
         <v>219</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -2614,7 +2614,7 @@
         <v>220</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -2622,7 +2622,7 @@
         <v>224</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -2630,7 +2630,7 @@
         <v>225</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -2638,7 +2638,7 @@
         <v>226</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -2646,7 +2646,7 @@
         <v>300</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -2654,7 +2654,7 @@
         <v>301</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -2662,7 +2662,7 @@
         <v>302</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -2670,7 +2670,7 @@
         <v>400</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -2678,7 +2678,7 @@
         <v>402</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -2686,7 +2686,7 @@
         <v>401</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -2694,25 +2694,25 @@
         <v>403</v>
       </c>
       <c r="B190" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" s="16" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B191" s="19"/>
-      <c r="C191" s="19"/>
+      <c r="B191" s="16"/>
+      <c r="C191" s="16"/>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B192" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B192" s="15" t="s">
+      <c r="C192" s="15" t="s">
         <v>135</v>
-      </c>
-      <c r="C192" s="15" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -2720,10 +2720,10 @@
         <v>1</v>
       </c>
       <c r="B193" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -2731,10 +2731,10 @@
         <v>2</v>
       </c>
       <c r="B194" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -2742,10 +2742,10 @@
         <v>3</v>
       </c>
       <c r="B195" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C195" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -2753,10 +2753,10 @@
         <v>4</v>
       </c>
       <c r="B196" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -2764,10 +2764,10 @@
         <v>5</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C197" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -2775,10 +2775,10 @@
         <v>6</v>
       </c>
       <c r="B198" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -2786,10 +2786,10 @@
         <v>7</v>
       </c>
       <c r="B199" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -2797,10 +2797,10 @@
         <v>8</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C200" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -2808,10 +2808,10 @@
         <v>9</v>
       </c>
       <c r="B201" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C201" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -2819,10 +2819,10 @@
         <v>10</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C202" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -2830,10 +2830,10 @@
         <v>11</v>
       </c>
       <c r="B203" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -2841,10 +2841,10 @@
         <v>12</v>
       </c>
       <c r="B204" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C204" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -2852,10 +2852,10 @@
         <v>13</v>
       </c>
       <c r="B205" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C205" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -2863,10 +2863,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -2874,10 +2874,10 @@
         <v>16</v>
       </c>
       <c r="B207" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C207" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -2885,10 +2885,10 @@
         <v>17</v>
       </c>
       <c r="B208" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C208" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -2896,10 +2896,10 @@
         <v>18</v>
       </c>
       <c r="B209" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -2907,10 +2907,10 @@
         <v>20</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C210" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -2918,10 +2918,10 @@
         <v>29</v>
       </c>
       <c r="B211" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C211" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -2929,10 +2929,10 @@
         <v>36</v>
       </c>
       <c r="B212" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -2940,10 +2940,10 @@
         <v>47</v>
       </c>
       <c r="B213" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C213" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -2951,10 +2951,10 @@
         <v>58</v>
       </c>
       <c r="B214" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C214" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -2962,10 +2962,10 @@
         <v>59</v>
       </c>
       <c r="B215" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C215" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -2973,10 +2973,10 @@
         <v>60</v>
       </c>
       <c r="B216" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -2984,10 +2984,10 @@
         <v>61</v>
       </c>
       <c r="B217" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C217" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -2995,10 +2995,10 @@
         <v>62</v>
       </c>
       <c r="B218" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C218" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -3006,10 +3006,10 @@
         <v>63</v>
       </c>
       <c r="B219" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -3017,10 +3017,10 @@
         <v>64</v>
       </c>
       <c r="B220" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C220" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -3028,10 +3028,10 @@
         <v>74</v>
       </c>
       <c r="B221" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C221" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -3039,10 +3039,10 @@
         <v>99</v>
       </c>
       <c r="B222" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -3050,10 +3050,10 @@
         <v>160</v>
       </c>
       <c r="B223" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C223" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -3061,10 +3061,10 @@
         <v>161</v>
       </c>
       <c r="B224" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C224" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -3072,10 +3072,10 @@
         <v>162</v>
       </c>
       <c r="B225" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -3083,10 +3083,10 @@
         <v>163</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C226" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -3094,10 +3094,10 @@
         <v>164</v>
       </c>
       <c r="B227" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C227" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -3105,10 +3105,10 @@
         <v>165</v>
       </c>
       <c r="B228" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -3116,10 +3116,10 @@
         <v>166</v>
       </c>
       <c r="B229" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C229" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -3127,10 +3127,10 @@
         <v>169</v>
       </c>
       <c r="B230" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C230" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -3138,10 +3138,10 @@
         <v>172</v>
       </c>
       <c r="B231" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C231" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -3149,10 +3149,10 @@
         <v>173</v>
       </c>
       <c r="B232" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C232" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -3160,10 +3160,10 @@
         <v>174</v>
       </c>
       <c r="B233" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C233" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -3171,10 +3171,10 @@
         <v>175</v>
       </c>
       <c r="B234" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C234" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -3182,10 +3182,10 @@
         <v>176</v>
       </c>
       <c r="B235" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C235" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -3193,10 +3193,10 @@
         <v>179</v>
       </c>
       <c r="B236" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C236" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -3204,10 +3204,10 @@
         <v>294</v>
       </c>
       <c r="B237" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C237" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -3215,10 +3215,10 @@
         <v>392</v>
       </c>
       <c r="B238" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C238" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -3226,10 +3226,10 @@
         <v>394</v>
       </c>
       <c r="B239" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C239" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -3237,10 +3237,10 @@
         <v>451</v>
       </c>
       <c r="B240" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C240" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -3248,10 +3248,10 @@
         <v>453</v>
       </c>
       <c r="B241" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C241" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -3259,14 +3259,21 @@
         <v>455</v>
       </c>
       <c r="B242" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C242" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A158:B158"/>
+    <mergeCell ref="A148:A154"/>
+    <mergeCell ref="A155:A157"/>
     <mergeCell ref="A191:C191"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A13"/>
@@ -3283,13 +3290,6 @@
     <mergeCell ref="A132:A133"/>
     <mergeCell ref="A134:A137"/>
     <mergeCell ref="A141:A147"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A158:B158"/>
-    <mergeCell ref="A148:A154"/>
-    <mergeCell ref="A155:A157"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" tooltip="http://15.252.130.159:12056/api/v1/basic/key" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
